--- a/Figure 2/Human weight & GTT/HUMAN-DATA-GTT.xlsx
+++ b/Figure 2/Human weight & GTT/HUMAN-DATA-GTT.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://api.box.com/wopi/files/1769572127926/WOPIServiceId_TP_BOX_2/WOPIUserId_-/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\florians\Documents\GitHub\Schoukroun2026-Human-Mice\Schoukroun-2026-Human-Mice\Figure 2\Human weight &amp; GTT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{08D63391-F5FE-462F-8CFC-BAAD0A7ED86B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1678D521-DC7E-4855-A499-E10E329138D8}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{616A3412-EAF0-4D2E-B5B7-3D9E2DBBC6DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2E9622B2-54B9-4675-AD40-68760FEB649A}"/>
   </bookViews>
@@ -1340,7 +1340,7 @@
         <v>7</v>
       </c>
       <c r="E21">
-        <v>28.871014079999998</v>
+        <v>24.4</v>
       </c>
       <c r="F21">
         <v>0</v>

--- a/Figure 2/Human weight & GTT/HUMAN-DATA-GTT.xlsx
+++ b/Figure 2/Human weight & GTT/HUMAN-DATA-GTT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\florians\Documents\GitHub\Schoukroun2026-Human-Mice\Schoukroun-2026-Human-Mice\Figure 2\Human weight &amp; GTT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{616A3412-EAF0-4D2E-B5B7-3D9E2DBBC6DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D60F345-1900-46D2-BAA3-53D2D98EC88B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2E9622B2-54B9-4675-AD40-68760FEB649A}"/>
   </bookViews>
@@ -2181,7 +2181,7 @@
         <v>23.9</v>
       </c>
       <c r="F45">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G45">
         <v>109</v>

--- a/Figure 2/Human weight & GTT/HUMAN-DATA-GTT.xlsx
+++ b/Figure 2/Human weight & GTT/HUMAN-DATA-GTT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\florians\Documents\GitHub\Schoukroun2026-Human-Mice\Schoukroun-2026-Human-Mice\Figure 2\Human weight &amp; GTT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D60F345-1900-46D2-BAA3-53D2D98EC88B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98CDE27E-FE84-4071-8DBB-FD81FA01D98B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2E9622B2-54B9-4675-AD40-68760FEB649A}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="64">
   <si>
     <t>id</t>
   </si>
@@ -48,9 +48,6 @@
   </si>
   <si>
     <t>BMI</t>
-  </si>
-  <si>
-    <t>Obesity</t>
   </si>
   <si>
     <t>MBWU06</t>
@@ -619,13 +616,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CAB8B03-AB5F-4531-99BD-4FF32AC96AAE}">
-  <dimension ref="A1:M49"/>
+  <dimension ref="A1:L49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="13" max="13" width="8.5703125" style="3" customWidth="1"/>
+    <col min="12" max="12" width="8.5703125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -639,7 +636,7 @@
         <v>3</v>
       </c>
       <c r="F1" t="s">
-        <v>4</v>
+        <v>53</v>
       </c>
       <c r="G1" t="s">
         <v>54</v>
@@ -654,1691 +651,1544 @@
         <v>57</v>
       </c>
       <c r="K1" t="s">
-        <v>58</v>
-      </c>
-      <c r="L1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>6</v>
-      </c>
-      <c r="C2" t="s">
-        <v>7</v>
       </c>
       <c r="E2">
         <v>20.8</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="G2">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="H2">
-        <v>106</v>
+        <v>151</v>
       </c>
       <c r="I2">
-        <v>151</v>
+        <v>111</v>
       </c>
       <c r="J2">
-        <v>111</v>
+        <v>85</v>
       </c>
       <c r="K2">
-        <v>85</v>
-      </c>
-      <c r="L2">
         <v>123</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E3">
         <v>19.3</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="G3">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="H3">
-        <v>105</v>
+        <v>129</v>
       </c>
       <c r="I3">
-        <v>129</v>
+        <v>178</v>
       </c>
       <c r="J3">
-        <v>178</v>
+        <v>122</v>
       </c>
       <c r="K3">
-        <v>122</v>
-      </c>
-      <c r="L3">
         <v>112</v>
       </c>
-      <c r="M3"/>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="L3"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>10</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3">
         <v>24.1</v>
       </c>
-      <c r="F4">
-        <v>1</v>
+      <c r="F4" s="3">
+        <v>92</v>
       </c>
       <c r="G4" s="3">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="H4" s="3">
-        <v>111</v>
+        <v>135</v>
       </c>
       <c r="I4" s="3">
-        <v>135</v>
+        <v>88</v>
       </c>
       <c r="J4" s="3">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="K4" s="3">
-        <v>90</v>
-      </c>
-      <c r="L4" s="3">
         <v>112</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3">
         <v>18.399999999999999</v>
       </c>
-      <c r="F5">
-        <v>0</v>
+      <c r="F5" s="3">
+        <v>90</v>
       </c>
       <c r="G5" s="3">
-        <v>90</v>
+        <v>129</v>
       </c>
       <c r="H5" s="3">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I5" s="3">
-        <v>128</v>
+        <v>92</v>
       </c>
       <c r="J5" s="3">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="K5" s="3">
-        <v>102</v>
-      </c>
-      <c r="L5" s="3">
         <v>110</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3">
         <v>21.6</v>
       </c>
-      <c r="F6">
-        <v>0</v>
+      <c r="F6" s="3">
+        <v>99</v>
       </c>
       <c r="G6" s="3">
-        <v>99</v>
+        <v>139</v>
       </c>
       <c r="H6" s="3">
-        <v>139</v>
+        <v>172</v>
       </c>
       <c r="I6" s="3">
-        <v>172</v>
+        <v>142</v>
       </c>
       <c r="J6" s="3">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="K6" s="3">
-        <v>133</v>
-      </c>
-      <c r="L6" s="3">
         <v>140</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E7">
         <v>19.710249059999999</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="G7">
-        <v>104</v>
+        <v>144</v>
       </c>
       <c r="H7">
-        <v>144</v>
+        <v>176</v>
       </c>
       <c r="I7">
-        <v>176</v>
+        <v>140</v>
       </c>
       <c r="J7">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="K7">
-        <v>134</v>
-      </c>
-      <c r="L7">
         <v>93</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E8">
         <v>20.152974650000001</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="G8">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="H8">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="I8">
-        <v>104</v>
+        <v>76</v>
       </c>
       <c r="J8">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="K8">
-        <v>89</v>
-      </c>
-      <c r="L8">
         <v>83</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E9">
         <v>23.146335310000001</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="G9">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="H9">
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="I9">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="J9">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="K9">
-        <v>109</v>
-      </c>
-      <c r="L9">
         <v>107</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E10">
         <v>21.5</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="G10">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="H10">
-        <v>113</v>
+        <v>139</v>
       </c>
       <c r="I10">
+        <v>161</v>
+      </c>
+      <c r="J10">
         <v>139</v>
       </c>
-      <c r="J10">
-        <v>161</v>
-      </c>
       <c r="K10">
-        <v>139</v>
-      </c>
-      <c r="L10">
         <v>120</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E11">
         <v>18.899999999999999</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="G11">
-        <v>88</v>
+        <v>131</v>
       </c>
       <c r="H11">
+        <v>143</v>
+      </c>
+      <c r="I11">
         <v>131</v>
       </c>
-      <c r="I11">
-        <v>143</v>
-      </c>
       <c r="J11">
-        <v>131</v>
+        <v>80</v>
       </c>
       <c r="K11">
-        <v>80</v>
-      </c>
-      <c r="L11">
         <v>69</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E12">
         <v>18</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="G12">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H12">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="I12">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="J12">
-        <v>84</v>
+        <v>57</v>
       </c>
       <c r="K12">
-        <v>57</v>
-      </c>
-      <c r="L12">
         <v>45</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E13">
         <v>15.5</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="G13">
-        <v>84</v>
+        <v>118</v>
       </c>
       <c r="H13">
-        <v>118</v>
+        <v>149</v>
       </c>
       <c r="I13">
-        <v>149</v>
+        <v>97</v>
       </c>
       <c r="J13">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="K13">
-        <v>122</v>
-      </c>
-      <c r="L13">
         <v>81</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E14">
         <v>21.5</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="G14">
-        <v>84</v>
+        <v>121</v>
       </c>
       <c r="H14">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="I14">
-        <v>137</v>
+        <v>81</v>
       </c>
       <c r="J14">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="K14">
-        <v>77</v>
-      </c>
-      <c r="L14">
         <v>67</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C15" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E15">
         <v>17</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="G15">
+        <v>124</v>
+      </c>
+      <c r="H15">
+        <v>155</v>
+      </c>
+      <c r="I15">
+        <v>108</v>
+      </c>
+      <c r="J15">
         <v>98</v>
       </c>
-      <c r="H15">
-        <v>124</v>
-      </c>
-      <c r="I15">
-        <v>155</v>
-      </c>
-      <c r="J15">
-        <v>108</v>
-      </c>
       <c r="K15">
-        <v>98</v>
-      </c>
-      <c r="L15">
         <v>113</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C16" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E16">
         <v>18.399999999999999</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="G16">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="H16">
-        <v>110</v>
+        <v>128</v>
       </c>
       <c r="I16">
-        <v>128</v>
+        <v>148</v>
       </c>
       <c r="J16">
-        <v>148</v>
+        <v>118</v>
       </c>
       <c r="K16">
-        <v>118</v>
-      </c>
-      <c r="L16">
         <v>114</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B17" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E17">
         <v>15.5</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="G17">
-        <v>95</v>
+        <v>118</v>
       </c>
       <c r="H17">
-        <v>118</v>
+        <v>147</v>
       </c>
       <c r="I17">
-        <v>147</v>
+        <v>124</v>
       </c>
       <c r="J17">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="K17">
-        <v>119</v>
-      </c>
-      <c r="L17">
         <v>101</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C18" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E18">
         <v>21.3</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="G18">
+        <v>117</v>
+      </c>
+      <c r="H18">
+        <v>129</v>
+      </c>
+      <c r="I18">
         <v>108</v>
       </c>
-      <c r="H18">
-        <v>117</v>
-      </c>
-      <c r="I18">
-        <v>129</v>
-      </c>
       <c r="J18">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="K18">
-        <v>116</v>
-      </c>
-      <c r="L18">
         <v>110</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B19" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C19" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E19">
         <v>18.100000000000001</v>
       </c>
-      <c r="F19">
-        <v>0</v>
+      <c r="F19" s="2">
+        <v>87</v>
       </c>
       <c r="G19" s="2">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="H19" s="2">
-        <v>96</v>
+        <v>123</v>
       </c>
       <c r="I19" s="2">
-        <v>123</v>
+        <v>97</v>
       </c>
       <c r="J19" s="2">
+        <v>106</v>
+      </c>
+      <c r="K19">
         <v>97</v>
       </c>
-      <c r="K19" s="2">
-        <v>106</v>
-      </c>
-      <c r="L19">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C20" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E20">
         <v>18.8</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="G20">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="H20">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="I20">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="J20">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="K20">
-        <v>78</v>
-      </c>
-      <c r="L20">
         <v>92</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B21" t="s">
+        <v>5</v>
+      </c>
+      <c r="C21" t="s">
         <v>6</v>
-      </c>
-      <c r="C21" t="s">
-        <v>7</v>
       </c>
       <c r="E21">
         <v>24.4</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="G21">
-        <v>96</v>
+        <v>121</v>
       </c>
       <c r="H21">
-        <v>121</v>
+        <v>191</v>
       </c>
       <c r="I21">
-        <v>191</v>
+        <v>122</v>
       </c>
       <c r="J21">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="K21">
-        <v>112</v>
-      </c>
-      <c r="L21">
         <v>53</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B22" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C22" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E22">
         <v>29.862258950000001</v>
       </c>
-      <c r="F22">
-        <v>1</v>
-      </c>
-      <c r="G22" s="1">
+      <c r="F22" s="1">
         <f>91</f>
         <v>91</v>
       </c>
+      <c r="G22" s="1">
+        <v>108</v>
+      </c>
       <c r="H22" s="1">
-        <v>108</v>
+        <v>143</v>
       </c>
       <c r="I22" s="1">
-        <v>143</v>
+        <v>173</v>
       </c>
       <c r="J22" s="1">
-        <v>173</v>
-      </c>
-      <c r="K22" s="1">
         <v>144</v>
       </c>
-      <c r="L22">
+      <c r="K22">
         <v>92</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" t="s">
+        <v>5</v>
+      </c>
+      <c r="C23" t="s">
         <v>31</v>
-      </c>
-      <c r="B23" t="s">
-        <v>6</v>
-      </c>
-      <c r="C23" t="s">
-        <v>32</v>
       </c>
       <c r="E23">
         <v>26.5</v>
       </c>
       <c r="F23">
-        <v>1</v>
+        <v>90</v>
       </c>
       <c r="G23">
-        <v>90</v>
+        <v>140</v>
       </c>
       <c r="H23">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="I23">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="J23">
-        <v>135</v>
+        <v>112</v>
       </c>
       <c r="K23">
-        <v>112</v>
-      </c>
-      <c r="L23">
         <v>92</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B24" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C24" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E24">
         <v>28</v>
       </c>
       <c r="F24">
-        <v>1</v>
+        <v>98</v>
       </c>
       <c r="G24">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="H24">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I24">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="J24">
-        <v>119</v>
+        <v>157</v>
       </c>
       <c r="K24">
-        <v>157</v>
-      </c>
-      <c r="L24">
         <v>135</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B25" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C25" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E25">
         <v>29.3</v>
       </c>
       <c r="F25">
-        <v>1</v>
+        <v>102</v>
       </c>
       <c r="G25">
-        <v>102</v>
+        <v>135</v>
       </c>
       <c r="H25">
-        <v>135</v>
+        <v>167</v>
       </c>
       <c r="I25">
-        <v>167</v>
+        <v>224</v>
       </c>
       <c r="J25">
-        <v>224</v>
+        <v>177</v>
       </c>
       <c r="K25">
-        <v>177</v>
-      </c>
-      <c r="L25">
         <v>163</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B26" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C26" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E26">
         <v>26.6</v>
       </c>
       <c r="F26">
-        <v>1</v>
+        <v>88</v>
       </c>
       <c r="G26">
-        <v>88</v>
+        <v>110</v>
       </c>
       <c r="H26">
-        <v>110</v>
+        <v>159</v>
       </c>
       <c r="I26">
-        <v>159</v>
+        <v>116</v>
       </c>
       <c r="J26">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="K26">
-        <v>132</v>
-      </c>
-      <c r="L26">
         <v>109</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>35</v>
+      </c>
+      <c r="B27" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27" t="s">
+        <v>14</v>
+      </c>
+      <c r="E27">
+        <v>24.9</v>
+      </c>
+      <c r="F27">
+        <v>89</v>
+      </c>
+      <c r="G27">
+        <v>108</v>
+      </c>
+      <c r="H27">
+        <v>134</v>
+      </c>
+      <c r="I27">
+        <v>86</v>
+      </c>
+      <c r="J27">
+        <v>99</v>
+      </c>
+      <c r="K27">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>36</v>
       </c>
-      <c r="B27" t="s">
-        <v>9</v>
-      </c>
-      <c r="C27" t="s">
-        <v>15</v>
-      </c>
-      <c r="E27">
-        <v>25.5</v>
-      </c>
-      <c r="F27">
-        <v>0</v>
-      </c>
-      <c r="G27">
-        <v>89</v>
-      </c>
-      <c r="H27">
-        <v>108</v>
-      </c>
-      <c r="I27">
-        <v>134</v>
-      </c>
-      <c r="J27">
-        <v>86</v>
-      </c>
-      <c r="K27">
-        <v>99</v>
-      </c>
-      <c r="L27">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>37</v>
-      </c>
       <c r="B28" t="s">
+        <v>5</v>
+      </c>
+      <c r="C28" t="s">
         <v>6</v>
-      </c>
-      <c r="C28" t="s">
-        <v>7</v>
       </c>
       <c r="E28">
         <v>46.721763090000003</v>
       </c>
       <c r="F28">
-        <v>1</v>
+        <v>96</v>
       </c>
       <c r="G28">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="H28">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="I28">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="J28">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="K28">
-        <v>125</v>
-      </c>
-      <c r="L28">
         <v>120</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B29" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C29" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E29">
         <v>43.1</v>
       </c>
       <c r="F29">
-        <v>1</v>
+        <v>86</v>
       </c>
       <c r="G29">
-        <v>86</v>
+        <v>114</v>
       </c>
       <c r="H29">
+        <v>131</v>
+      </c>
+      <c r="I29">
+        <v>119</v>
+      </c>
+      <c r="J29">
         <v>114</v>
       </c>
-      <c r="I29">
-        <v>131</v>
-      </c>
-      <c r="J29">
+      <c r="K29">
         <v>119</v>
       </c>
-      <c r="K29">
-        <v>114</v>
-      </c>
-      <c r="L29">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B30" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C30" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E30">
         <v>31.7</v>
       </c>
       <c r="F30">
-        <v>1</v>
+        <v>81</v>
       </c>
       <c r="G30">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="H30">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="I30">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="J30">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="K30">
-        <v>117</v>
-      </c>
-      <c r="L30">
         <v>105</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B31" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C31" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E31">
         <v>35.78</v>
       </c>
       <c r="F31">
-        <v>1</v>
+        <v>92</v>
       </c>
       <c r="G31">
-        <v>92</v>
+        <v>123</v>
       </c>
       <c r="H31">
-        <v>123</v>
+        <v>148</v>
       </c>
       <c r="I31">
-        <v>148</v>
+        <v>72</v>
       </c>
       <c r="J31">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="K31">
-        <v>84</v>
-      </c>
-      <c r="L31">
         <v>133</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B32" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C32" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E32">
         <v>45.16</v>
       </c>
       <c r="F32">
-        <v>1</v>
+        <v>98</v>
       </c>
       <c r="G32">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="H32">
-        <v>104</v>
+        <v>125</v>
       </c>
       <c r="I32">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="J32">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="K32">
-        <v>123</v>
-      </c>
-      <c r="L32">
         <v>108</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B33" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C33" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E33">
         <v>35.93</v>
       </c>
       <c r="F33">
-        <v>1</v>
+        <v>93</v>
       </c>
       <c r="G33">
-        <v>93</v>
+        <v>122</v>
       </c>
       <c r="H33">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="I33">
-        <v>130</v>
+        <v>92</v>
       </c>
       <c r="J33">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="K33">
-        <v>87</v>
-      </c>
-      <c r="L33">
         <v>98</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B34" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C34" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E34">
         <v>34.700000000000003</v>
       </c>
       <c r="F34">
-        <v>1</v>
+        <v>111</v>
       </c>
       <c r="G34">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="H34">
-        <v>119</v>
+        <v>137</v>
       </c>
       <c r="I34">
-        <v>137</v>
+        <v>151</v>
       </c>
       <c r="J34">
-        <v>151</v>
+        <v>129</v>
       </c>
       <c r="K34">
-        <v>129</v>
-      </c>
-      <c r="L34">
         <v>141</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C35" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E35">
         <v>31.5</v>
       </c>
       <c r="F35">
-        <v>1</v>
+        <v>93</v>
       </c>
       <c r="G35">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="H35">
+        <v>116</v>
+      </c>
+      <c r="I35">
         <v>109</v>
       </c>
-      <c r="I35">
-        <v>116</v>
-      </c>
       <c r="J35">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="K35">
-        <v>125</v>
-      </c>
-      <c r="L35">
         <v>84</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B36" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C36" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E36">
         <v>36.700000000000003</v>
       </c>
       <c r="F36">
-        <v>1</v>
+        <v>104</v>
       </c>
       <c r="G36">
-        <v>104</v>
+        <v>132</v>
       </c>
       <c r="H36">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="I36">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="J36">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="K36">
-        <v>145</v>
-      </c>
-      <c r="L36">
         <v>125</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B37" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C37" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E37">
         <v>50.3</v>
       </c>
       <c r="F37">
-        <v>1</v>
+        <v>89</v>
       </c>
       <c r="G37">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="H37">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="I37">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="J37">
+        <v>94</v>
+      </c>
+      <c r="K37">
         <v>100</v>
       </c>
-      <c r="K37">
-        <v>94</v>
-      </c>
-      <c r="L37">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B38" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C38" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E38">
         <v>40.1</v>
       </c>
       <c r="F38">
-        <v>1</v>
+        <v>85</v>
       </c>
       <c r="G38">
-        <v>85</v>
+        <v>136</v>
       </c>
       <c r="H38">
-        <v>136</v>
+        <v>179</v>
       </c>
       <c r="I38">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="J38">
-        <v>176</v>
+        <v>152</v>
       </c>
       <c r="K38">
-        <v>152</v>
-      </c>
-      <c r="L38">
         <v>170</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B39" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C39" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E39">
         <v>26.7</v>
       </c>
       <c r="F39">
-        <v>1</v>
+        <v>112</v>
       </c>
       <c r="G39">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H39">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="I39">
-        <v>129</v>
+        <v>158</v>
       </c>
       <c r="J39">
-        <v>158</v>
+        <v>178</v>
       </c>
       <c r="K39">
-        <v>178</v>
-      </c>
-      <c r="L39">
         <v>148</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B40" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C40" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E40">
         <v>32.700000000000003</v>
       </c>
       <c r="F40">
-        <v>1</v>
+        <v>93</v>
       </c>
       <c r="G40">
-        <v>93</v>
+        <v>118</v>
       </c>
       <c r="H40">
-        <v>118</v>
+        <v>168</v>
       </c>
       <c r="I40">
-        <v>168</v>
+        <v>203</v>
       </c>
       <c r="J40">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="K40">
-        <v>219</v>
-      </c>
-      <c r="L40">
         <v>175</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B41" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C41" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E41">
         <v>50.9</v>
       </c>
       <c r="F41">
-        <v>1</v>
+        <v>122</v>
       </c>
       <c r="G41">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="H41">
-        <v>137</v>
+        <v>180</v>
       </c>
       <c r="I41">
-        <v>180</v>
+        <v>229</v>
       </c>
       <c r="J41">
-        <v>229</v>
+        <v>209</v>
       </c>
       <c r="K41">
-        <v>209</v>
-      </c>
-      <c r="L41">
         <v>189</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B42" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C42" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E42">
         <v>44.5</v>
       </c>
       <c r="F42">
-        <v>1</v>
+        <v>107</v>
       </c>
       <c r="G42">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="H42">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="I42">
-        <v>127</v>
+        <v>157</v>
       </c>
       <c r="J42">
-        <v>157</v>
+        <v>191</v>
       </c>
       <c r="K42">
-        <v>191</v>
-      </c>
-      <c r="L42">
         <v>158</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B43" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C43" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E43">
         <v>45.6</v>
       </c>
       <c r="F43">
-        <v>1</v>
+        <v>105</v>
       </c>
       <c r="G43">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="H43">
-        <v>109</v>
+        <v>144</v>
       </c>
       <c r="I43">
-        <v>144</v>
+        <v>162</v>
       </c>
       <c r="J43">
-        <v>162</v>
+        <v>136</v>
       </c>
       <c r="K43">
-        <v>136</v>
-      </c>
-      <c r="L43">
         <v>132</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B44" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C44" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E44">
         <v>29</v>
       </c>
       <c r="F44">
-        <v>1</v>
+        <v>98</v>
       </c>
       <c r="G44">
-        <v>98</v>
+        <v>138</v>
       </c>
       <c r="H44">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="I44">
-        <v>151</v>
+        <v>112</v>
       </c>
       <c r="J44">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="K44">
-        <v>101</v>
-      </c>
-      <c r="L44">
         <v>113</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B45" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C45" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E45">
         <v>23.9</v>
       </c>
       <c r="F45">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="G45">
-        <v>109</v>
+        <v>128</v>
       </c>
       <c r="H45">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="I45">
-        <v>136</v>
+        <v>80</v>
       </c>
       <c r="J45">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="K45">
-        <v>88</v>
-      </c>
-      <c r="L45">
         <v>82</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B46" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C46" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E46">
         <v>25.1</v>
       </c>
       <c r="F46">
-        <v>1</v>
+        <v>89</v>
       </c>
       <c r="G46">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="H46">
-        <v>107</v>
+        <v>153</v>
       </c>
       <c r="I46">
-        <v>153</v>
+        <v>109</v>
       </c>
       <c r="J46">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="K46">
-        <v>115</v>
-      </c>
-      <c r="L46">
         <v>122</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B47" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C47" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E47">
         <v>27.4</v>
       </c>
       <c r="F47">
-        <v>1</v>
+        <v>93</v>
       </c>
       <c r="G47">
-        <v>93</v>
+        <v>118</v>
       </c>
       <c r="H47">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="I47">
-        <v>137</v>
+        <v>86</v>
       </c>
       <c r="J47">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="K47">
-        <v>101</v>
-      </c>
-      <c r="L47">
         <v>79</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B48" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C48" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E48">
         <v>34.5</v>
       </c>
       <c r="F48">
-        <v>1</v>
+        <v>98</v>
       </c>
       <c r="G48">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="H48">
-        <v>101</v>
+        <v>147</v>
       </c>
       <c r="I48">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="J48">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="K48">
-        <v>148</v>
-      </c>
-      <c r="L48">
         <v>145</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B49" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C49" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E49">
         <v>38.200000000000003</v>
       </c>
       <c r="F49">
-        <v>1</v>
+        <v>88</v>
       </c>
       <c r="G49">
-        <v>88</v>
+        <v>131</v>
       </c>
       <c r="H49">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="I49">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="J49">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="K49">
-        <v>135</v>
-      </c>
-      <c r="L49">
         <v>108</v>
       </c>
     </row>
